--- a/onlineCompcorImplementation/results/kscSynthDataset.xlsx
+++ b/onlineCompcorImplementation/results/kscSynthDataset.xlsx
@@ -465,26 +465,26 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00089211961011067</v>
+        <v>1.652073352056e-05</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00146272180045121</v>
+        <v>2.896478812774e-05</v>
       </c>
       <c r="D2" t="n">
-        <v>4.395724263562654</v>
+        <v>1.537187658337917</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.809484351466615</v>
+        <v>-0.3242384694860216</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7627224203800828</v>
+        <v>0.9999943187021736</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.6959813022058214</v>
+        <v>-0.4041739582825991</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -495,26 +495,26 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7972782091524864</v>
+        <v>0.799564318604464</v>
       </c>
       <c r="C3" t="n">
-        <v>0.7240479319803135</v>
+        <v>0.7397077370603085</v>
       </c>
       <c r="D3" t="n">
-        <v>3.350735583803054</v>
+        <v>3.094511333841504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7905378245824863</v>
+        <v>0.7475706095004031</v>
       </c>
       <c r="F3" t="n">
-        <v>0.6531961737880122</v>
+        <v>0.5845641257904433</v>
       </c>
       <c r="G3" t="n">
-        <v>0.8278155976895829</v>
+        <v>0.7873153688078518</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -525,26 +525,26 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8339028750312412</v>
+        <v>0.8910154744203977</v>
       </c>
       <c r="C4" t="n">
-        <v>0.7868661130217655</v>
+        <v>0.8440676538810776</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2879106905600148</v>
+        <v>0.2874102313131758</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8083300428086495</v>
+        <v>0.890335074836328</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7998673612066989</v>
+        <v>0.8664774250874285</v>
       </c>
       <c r="G4" t="n">
-        <v>0.8727572474710856</v>
+        <v>0.9220606499519557</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -555,26 +555,26 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8985553889361919</v>
+        <v>0.8039953699585287</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8557477244856269</v>
+        <v>0.7432767346457733</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05326363144688817</v>
+        <v>0.05400749463438276</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9094688928370712</v>
+        <v>0.6093745138115961</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9011702183856649</v>
+        <v>0.2901694783353826</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9354738333338757</v>
+        <v>0.6455485223170351</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -585,26 +585,26 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7834869973355021</v>
+        <v>0.6762388432097668</v>
       </c>
       <c r="C6" t="n">
-        <v>0.715529675038251</v>
+        <v>0.6184872919050513</v>
       </c>
       <c r="D6" t="n">
-        <v>23.91773641731701</v>
+        <v>24.55161798998138</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7708915358075382</v>
+        <v>0.3925463826515103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.688555444341609</v>
+        <v>0.003728178356317342</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8306302600021064</v>
+        <v>0.4379273084962533</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -615,26 +615,26 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8770188124557858</v>
+        <v>0.835299512426557</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8257382927914406</v>
+        <v>0.7691182987506945</v>
       </c>
       <c r="D7" t="n">
-        <v>0.03762417097754026</v>
+        <v>0.034947455732596</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8813483683856378</v>
+        <v>0.83291343456331</v>
       </c>
       <c r="F7" t="n">
-        <v>0.843292893889229</v>
+        <v>0.7770029577288198</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8945059627066803</v>
+        <v>0.8438361863811921</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -645,26 +645,26 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7259570376206754</v>
+        <v>0.7658589510605041</v>
       </c>
       <c r="C8" t="n">
-        <v>0.6672952583032233</v>
+        <v>0.7021310812379904</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2878869578316642</v>
+        <v>0.287340523633405</v>
       </c>
       <c r="E8" t="n">
-        <v>0.609632985921752</v>
+        <v>0.6212491799343089</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5323725446540942</v>
+        <v>0.5200350093128089</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7044284666259213</v>
+        <v>0.7142029392442806</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -675,26 +675,26 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8593014906784939</v>
+        <v>0.8972271643219933</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8049421142108586</v>
+        <v>0.8499122795159562</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01200148696040652</v>
+        <v>0.00691691329316514</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8530232373602328</v>
+        <v>0.8600772645940997</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7278409207550676</v>
+        <v>0.7676097144197198</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8746235855039952</v>
+        <v>0.8907185934374053</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -705,26 +705,26 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8952445703973873</v>
+        <v>0.8646572795011586</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8463602451357246</v>
+        <v>0.8045616759013472</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00162688916015331</v>
+        <v>0.00100905166567283</v>
       </c>
       <c r="E10" t="n">
-        <v>0.8925427165675154</v>
+        <v>0.8380571833348966</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8321655686765648</v>
+        <v>0.7193780293016363</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9198972906206533</v>
+        <v>0.8666304329210359</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -735,26 +735,26 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8402753243782486</v>
+        <v>0.9189985258422397</v>
       </c>
       <c r="C11" t="n">
-        <v>0.7902984325492859</v>
+        <v>0.8792521164110203</v>
       </c>
       <c r="D11" t="n">
-        <v>6.818805731702736</v>
+        <v>2.932961144099852</v>
       </c>
       <c r="E11" t="n">
-        <v>0.5823835570330234</v>
+        <v>0.9139324333961106</v>
       </c>
       <c r="F11" t="n">
-        <v>0.2331710977408832</v>
+        <v>0.8486291493829754</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6154569934467748</v>
+        <v>0.9341400061572518</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>atis</t>
+          <t>yahoo</t>
         </is>
       </c>
     </row>
@@ -1065,26 +1065,26 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0008888366438341299</v>
+        <v>0.00104080621179578</v>
       </c>
       <c r="C22" t="n">
-        <v>0.00140334115735573</v>
+        <v>0.00182478165204805</v>
       </c>
       <c r="D22" t="n">
-        <v>3.629577349653022</v>
+        <v>1.29844800508057</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4976122770850339</v>
+        <v>-0.9372059139263799</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7315670994861814</v>
+        <v>0.8507463389496914</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3866429930945717</v>
+        <v>-0.849191211561905</v>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1095,26 +1095,26 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8152995759678396</v>
+        <v>0.7915912643444445</v>
       </c>
       <c r="C23" t="n">
-        <v>0.766179804722847</v>
+        <v>0.719671816228225</v>
       </c>
       <c r="D23" t="n">
-        <v>3.076774734745236</v>
+        <v>3.130743645301167</v>
       </c>
       <c r="E23" t="n">
-        <v>0.7643491335825503</v>
+        <v>0.7436706138012272</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5436335478880151</v>
+        <v>0.619139152936413</v>
       </c>
       <c r="G23" t="n">
-        <v>0.7698822363831679</v>
+        <v>0.7942274651293951</v>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1125,26 +1125,26 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8846746898126379</v>
+        <v>0.8846912105461584</v>
       </c>
       <c r="C24" t="n">
-        <v>0.837888753177177</v>
+        <v>0.8405409622767411</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2873989328511951</v>
+        <v>0.2874953783992834</v>
       </c>
       <c r="E24" t="n">
-        <v>0.8814096434293563</v>
+        <v>0.8352150783562517</v>
       </c>
       <c r="F24" t="n">
-        <v>0.8571183763866586</v>
+        <v>0.810099523328619</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9081822844510705</v>
+        <v>0.8859002020870177</v>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1155,26 +1155,26 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8546360778931406</v>
+        <v>0.8340278395540249</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8031414529176489</v>
+        <v>0.7698049523525573</v>
       </c>
       <c r="D25" t="n">
-        <v>0.05333438079718607</v>
+        <v>0.05230426479677074</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7087869318073442</v>
+        <v>0.7275587739071838</v>
       </c>
       <c r="F25" t="n">
-        <v>0.5002163879338758</v>
+        <v>0.5398268822283023</v>
       </c>
       <c r="G25" t="n">
-        <v>0.7602831988472198</v>
+        <v>0.7783868997546373</v>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1185,26 +1185,26 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7642133377388622</v>
+        <v>0.7022199206157573</v>
       </c>
       <c r="C26" t="n">
-        <v>0.7137596782881128</v>
+        <v>0.6559390849073805</v>
       </c>
       <c r="D26" t="n">
-        <v>24.62180168443162</v>
+        <v>24.67305666065167</v>
       </c>
       <c r="E26" t="n">
-        <v>0.5744333056204667</v>
+        <v>0.4040839897124238</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2905002566702849</v>
+        <v>0.02552744322533394</v>
       </c>
       <c r="G26" t="n">
-        <v>0.6356721240031273</v>
+        <v>0.4493916682687953</v>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1215,26 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.9179310322916799</v>
+        <v>0.7501769624725184</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8751574947918974</v>
+        <v>0.6811899278408025</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0344073262118625</v>
+        <v>0.03544709714181936</v>
       </c>
       <c r="E27" t="n">
-        <v>0.9069163460089333</v>
+        <v>0.6938630702686907</v>
       </c>
       <c r="F27" t="n">
-        <v>0.8724252545368418</v>
+        <v>0.6474829029671523</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9205467678543979</v>
+        <v>0.7434779767251887</v>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1245,26 +1245,26 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7665203099120166</v>
+        <v>0.7090929693688657</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7175632657224735</v>
+        <v>0.6522632532249242</v>
       </c>
       <c r="D28" t="n">
-        <v>0.2875674111117799</v>
+        <v>0.2871446992391608</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5955511038706331</v>
+        <v>0.5903553701381405</v>
       </c>
       <c r="F28" t="n">
-        <v>0.5055273129221656</v>
+        <v>0.5333763067591557</v>
       </c>
       <c r="G28" t="n">
-        <v>0.6781716214057788</v>
+        <v>0.6886895386343974</v>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1275,26 +1275,26 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7596965056530561</v>
+        <v>0.9254251970838787</v>
       </c>
       <c r="C29" t="n">
-        <v>0.6908491365355065</v>
+        <v>0.8879111256846424</v>
       </c>
       <c r="D29" t="n">
-        <v>0.01143419357032245</v>
+        <v>0.00316484863954621</v>
       </c>
       <c r="E29" t="n">
-        <v>0.7339086745824122</v>
+        <v>0.934065531785516</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5738902821541203</v>
+        <v>0.8838510867024645</v>
       </c>
       <c r="G29" t="n">
-        <v>0.7818905167704492</v>
+        <v>0.9489593888775207</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1305,26 +1305,26 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8653247806766724</v>
+        <v>0.9686106063109202</v>
       </c>
       <c r="C30" t="n">
-        <v>0.808878445882021</v>
+        <v>0.9462558356289652</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00165391031608374</v>
+        <v>0.00037623663048139</v>
       </c>
       <c r="E30" t="n">
-        <v>0.8793908262818285</v>
+        <v>0.9635915513003313</v>
       </c>
       <c r="F30" t="n">
-        <v>0.821612450855483</v>
+        <v>0.9380483550268159</v>
       </c>
       <c r="G30" t="n">
-        <v>0.9121293553798436</v>
+        <v>0.9727528827466606</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1335,26 +1335,26 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.4897656173882838</v>
+        <v>0.751422689321252</v>
       </c>
       <c r="C31" t="n">
-        <v>0.4830483270013501</v>
+        <v>0.6835472979259376</v>
       </c>
       <c r="D31" t="n">
-        <v>6.36664545687295</v>
+        <v>2.722393821507904</v>
       </c>
       <c r="E31" t="n">
-        <v>0.08109863289559303</v>
+        <v>0.6657621225102027</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.09818630793501029</v>
+        <v>0.4099992267592877</v>
       </c>
       <c r="G31" t="n">
-        <v>0.1272900398116057</v>
+        <v>0.7078377740811137</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>clinc150</t>
+          <t>medicalAbstracts</t>
         </is>
       </c>
     </row>
@@ -1365,26 +1365,26 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>4.956220056169e-05</v>
+        <v>0</v>
       </c>
       <c r="C32" t="n">
-        <v>8.689436438323001e-05</v>
+        <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>1.64878514191245</v>
+        <v>1.787478659058566</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.5586091155044843</v>
+        <v>-0.5579825969091865</v>
       </c>
       <c r="F32" t="n">
-        <v>0.9480101249712269</v>
+        <v>0.998575344309926</v>
       </c>
       <c r="G32" t="n">
-        <v>-0.4302643439198702</v>
+        <v>-0.4160078111353775</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1395,26 +1395,26 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.787055263971669</v>
+        <v>0.7570261832445874</v>
       </c>
       <c r="C33" t="n">
-        <v>0.7193066370657968</v>
+        <v>0.6904804102063866</v>
       </c>
       <c r="D33" t="n">
-        <v>3.147568300179218</v>
+        <v>3.171587915511444</v>
       </c>
       <c r="E33" t="n">
-        <v>0.7562806050934462</v>
+        <v>0.7274251316293344</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5487746253654227</v>
+        <v>0.6018007620176323</v>
       </c>
       <c r="G33" t="n">
-        <v>0.7767629806210856</v>
+        <v>0.775731166995992</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1425,26 +1425,26 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8582409866690388</v>
+        <v>0.9369828269093097</v>
       </c>
       <c r="C34" t="n">
-        <v>0.806964557451171</v>
+        <v>0.9060935625740874</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2875257597432571</v>
+        <v>0.2870783284541892</v>
       </c>
       <c r="E34" t="n">
-        <v>0.8421962474171353</v>
+        <v>0.9091169401796315</v>
       </c>
       <c r="F34" t="n">
-        <v>0.8298596586822343</v>
+        <v>0.8727741207723438</v>
       </c>
       <c r="G34" t="n">
-        <v>0.8943727476581658</v>
+        <v>0.9309445618620072</v>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1455,26 +1455,26 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8643502692032348</v>
+        <v>0.8016663701406803</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8145123145129167</v>
+        <v>0.7367646473766024</v>
       </c>
       <c r="D35" t="n">
-        <v>0.05166617002853256</v>
+        <v>0.05289801260940287</v>
       </c>
       <c r="E35" t="n">
-        <v>0.8340277743129106</v>
+        <v>0.6062483467787279</v>
       </c>
       <c r="F35" t="n">
-        <v>0.7642540694659509</v>
+        <v>0.3170698285638466</v>
       </c>
       <c r="G35" t="n">
-        <v>0.876582109105865</v>
+        <v>0.6576505141837572</v>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1485,26 +1485,26 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.7579197854846293</v>
+        <v>0.6670930286740628</v>
       </c>
       <c r="C36" t="n">
-        <v>0.6980569298133102</v>
+        <v>0.630562911754764</v>
       </c>
       <c r="D36" t="n">
-        <v>24.82748105517844</v>
+        <v>23.97036028969939</v>
       </c>
       <c r="E36" t="n">
-        <v>0.724567988734647</v>
+        <v>0.3537579697148117</v>
       </c>
       <c r="F36" t="n">
-        <v>0.6161429724142076</v>
+        <v>-0.02045306247907295</v>
       </c>
       <c r="G36" t="n">
-        <v>0.7948442333279333</v>
+        <v>0.4051809994447909</v>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1515,26 +1515,26 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8217297419800311</v>
+        <v>0.8132837287719166</v>
       </c>
       <c r="C37" t="n">
-        <v>0.753526750849542</v>
+        <v>0.7430570236599614</v>
       </c>
       <c r="D37" t="n">
-        <v>0.03388586007287284</v>
+        <v>0.03372062167861598</v>
       </c>
       <c r="E37" t="n">
-        <v>0.8226725565584385</v>
+        <v>0.8108318225849596</v>
       </c>
       <c r="F37" t="n">
-        <v>0.7466732775740352</v>
+        <v>0.7785064241393862</v>
       </c>
       <c r="G37" t="n">
-        <v>0.8486213719879085</v>
+        <v>0.8505220414075534</v>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1545,26 +1545,26 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.6983013297072442</v>
+        <v>0.7713371627546417</v>
       </c>
       <c r="C38" t="n">
-        <v>0.6444345646817389</v>
+        <v>0.7212892872211218</v>
       </c>
       <c r="D38" t="n">
-        <v>0.2875176632810553</v>
+        <v>0.2872753014844515</v>
       </c>
       <c r="E38" t="n">
-        <v>0.5318367146060889</v>
+        <v>0.6406786462385636</v>
       </c>
       <c r="F38" t="n">
-        <v>0.4946255682134423</v>
+        <v>0.5617582084159545</v>
       </c>
       <c r="G38" t="n">
-        <v>0.666444458423916</v>
+        <v>0.7223318415975475</v>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1575,26 +1575,26 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.7608526392930821</v>
+        <v>0.8901628563077433</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6953079240660907</v>
+        <v>0.8440997720721373</v>
       </c>
       <c r="D39" t="n">
-        <v>0.00710288943866135</v>
+        <v>0.009140480894348151</v>
       </c>
       <c r="E39" t="n">
-        <v>0.73278502515823</v>
+        <v>0.849437233967185</v>
       </c>
       <c r="F39" t="n">
-        <v>0.5634318822607469</v>
+        <v>0.7330209835000063</v>
       </c>
       <c r="G39" t="n">
-        <v>0.7737342321612199</v>
+        <v>0.8751359065264276</v>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1605,26 +1605,26 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8559280839761594</v>
+        <v>0.8437157671339069</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8040882840838266</v>
+        <v>0.7894008143539647</v>
       </c>
       <c r="D40" t="n">
-        <v>0.0007249781767510201</v>
+        <v>0.00143306536705956</v>
       </c>
       <c r="E40" t="n">
-        <v>0.8196113473661391</v>
+        <v>0.8065543688822804</v>
       </c>
       <c r="F40" t="n">
-        <v>0.6824371564544203</v>
+        <v>0.6697178937696968</v>
       </c>
       <c r="G40" t="n">
-        <v>0.8496949728216818</v>
+        <v>0.8395054200296737</v>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1635,26 +1635,26 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.883818894635845</v>
+        <v>0.9045159848687025</v>
       </c>
       <c r="C41" t="n">
-        <v>0.8480012893674259</v>
+        <v>0.8621527952088308</v>
       </c>
       <c r="D41" t="n">
-        <v>2.964079712475722</v>
+        <v>3.313321208615281</v>
       </c>
       <c r="E41" t="n">
-        <v>0.8078311867680248</v>
+        <v>0.8161338182023152</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6108978286530231</v>
+        <v>0.6347852442742015</v>
       </c>
       <c r="G41" t="n">
-        <v>0.8241501296232097</v>
+        <v>0.8409225765325237</v>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>clinicalDialogueSummarizations</t>
+          <t>huffPostNews</t>
         </is>
       </c>
     </row>
@@ -1665,26 +1665,26 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>0.0008888366438341299</v>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>0.00140334115735573</v>
       </c>
       <c r="D42" t="n">
-        <v>1.787478659058566</v>
+        <v>3.629577349653022</v>
       </c>
       <c r="E42" t="n">
-        <v>-0.5579825969091865</v>
+        <v>-0.4976122770850339</v>
       </c>
       <c r="F42" t="n">
-        <v>0.998575344309926</v>
+        <v>0.7315670994861814</v>
       </c>
       <c r="G42" t="n">
-        <v>-0.4160078111353775</v>
+        <v>-0.3866429930945717</v>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1695,26 +1695,26 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.7570261832445874</v>
+        <v>0.8152995759678396</v>
       </c>
       <c r="C43" t="n">
-        <v>0.6904804102063866</v>
+        <v>0.766179804722847</v>
       </c>
       <c r="D43" t="n">
-        <v>3.171587915511444</v>
+        <v>3.076774734745236</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7274251316293344</v>
+        <v>0.7643491335825503</v>
       </c>
       <c r="F43" t="n">
-        <v>0.6018007620176323</v>
+        <v>0.5436335478880151</v>
       </c>
       <c r="G43" t="n">
-        <v>0.775731166995992</v>
+        <v>0.7698822363831679</v>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1725,26 +1725,26 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.9369828269093097</v>
+        <v>0.8846746898126379</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9060935625740874</v>
+        <v>0.837888753177177</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2870783284541892</v>
+        <v>0.2873989328511951</v>
       </c>
       <c r="E44" t="n">
-        <v>0.9091169401796315</v>
+        <v>0.8814096434293563</v>
       </c>
       <c r="F44" t="n">
-        <v>0.8727741207723438</v>
+        <v>0.8571183763866586</v>
       </c>
       <c r="G44" t="n">
-        <v>0.9309445618620072</v>
+        <v>0.9081822844510705</v>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1755,26 +1755,26 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8016663701406803</v>
+        <v>0.8546360778931406</v>
       </c>
       <c r="C45" t="n">
-        <v>0.7367646473766024</v>
+        <v>0.8031414529176489</v>
       </c>
       <c r="D45" t="n">
-        <v>0.05289801260940287</v>
+        <v>0.05333438079718607</v>
       </c>
       <c r="E45" t="n">
-        <v>0.6062483467787279</v>
+        <v>0.7087869318073442</v>
       </c>
       <c r="F45" t="n">
-        <v>0.3170698285638466</v>
+        <v>0.5002163879338758</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6576505141837572</v>
+        <v>0.7602831988472198</v>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1785,26 +1785,26 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.6670930286740628</v>
+        <v>0.7642133377388622</v>
       </c>
       <c r="C46" t="n">
-        <v>0.630562911754764</v>
+        <v>0.7137596782881128</v>
       </c>
       <c r="D46" t="n">
-        <v>23.97036028969939</v>
+        <v>24.62180168443162</v>
       </c>
       <c r="E46" t="n">
-        <v>0.3537579697148117</v>
+        <v>0.5744333056204667</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.02045306247907295</v>
+        <v>0.2905002566702849</v>
       </c>
       <c r="G46" t="n">
-        <v>0.4051809994447909</v>
+        <v>0.6356721240031273</v>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1815,26 +1815,26 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8132837287719166</v>
+        <v>0.9179310322916799</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7430570236599614</v>
+        <v>0.8751574947918974</v>
       </c>
       <c r="D47" t="n">
-        <v>0.03372062167861598</v>
+        <v>0.0344073262118625</v>
       </c>
       <c r="E47" t="n">
-        <v>0.8108318225849596</v>
+        <v>0.9069163460089333</v>
       </c>
       <c r="F47" t="n">
-        <v>0.7785064241393862</v>
+        <v>0.8724252545368418</v>
       </c>
       <c r="G47" t="n">
-        <v>0.8505220414075534</v>
+        <v>0.9205467678543979</v>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1845,26 +1845,26 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.7713371627546417</v>
+        <v>0.7665203099120166</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7212892872211218</v>
+        <v>0.7175632657224735</v>
       </c>
       <c r="D48" t="n">
-        <v>0.2872753014844515</v>
+        <v>0.2875674111117799</v>
       </c>
       <c r="E48" t="n">
-        <v>0.6406786462385636</v>
+        <v>0.5955511038706331</v>
       </c>
       <c r="F48" t="n">
-        <v>0.5617582084159545</v>
+        <v>0.5055273129221656</v>
       </c>
       <c r="G48" t="n">
-        <v>0.7223318415975475</v>
+        <v>0.6781716214057788</v>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1875,26 +1875,26 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8901628563077433</v>
+        <v>0.7596965056530561</v>
       </c>
       <c r="C49" t="n">
-        <v>0.8440997720721373</v>
+        <v>0.6908491365355065</v>
       </c>
       <c r="D49" t="n">
-        <v>0.009140480894348151</v>
+        <v>0.01143419357032245</v>
       </c>
       <c r="E49" t="n">
-        <v>0.849437233967185</v>
+        <v>0.7339086745824122</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7330209835000063</v>
+        <v>0.5738902821541203</v>
       </c>
       <c r="G49" t="n">
-        <v>0.8751359065264276</v>
+        <v>0.7818905167704492</v>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1905,26 +1905,26 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8437157671339069</v>
+        <v>0.8653247806766724</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7894008143539647</v>
+        <v>0.808878445882021</v>
       </c>
       <c r="D50" t="n">
-        <v>0.00143306536705956</v>
+        <v>0.00165391031608374</v>
       </c>
       <c r="E50" t="n">
-        <v>0.8065543688822804</v>
+        <v>0.8793908262818285</v>
       </c>
       <c r="F50" t="n">
-        <v>0.6697178937696968</v>
+        <v>0.821612450855483</v>
       </c>
       <c r="G50" t="n">
-        <v>0.8395054200296737</v>
+        <v>0.9121293553798436</v>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1935,26 +1935,26 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.9045159848687025</v>
+        <v>0.4897656173882838</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8621527952088308</v>
+        <v>0.4830483270013501</v>
       </c>
       <c r="D51" t="n">
-        <v>3.313321208615281</v>
+        <v>6.36664545687295</v>
       </c>
       <c r="E51" t="n">
-        <v>0.8161338182023152</v>
+        <v>0.08109863289559303</v>
       </c>
       <c r="F51" t="n">
-        <v>0.6347852442742015</v>
+        <v>-0.09818630793501029</v>
       </c>
       <c r="G51" t="n">
-        <v>0.8409225765325237</v>
+        <v>0.1272900398116057</v>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>huffPostNews</t>
+          <t>clinc150</t>
         </is>
       </c>
     </row>
@@ -1965,26 +1965,26 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.00104080621179578</v>
+        <v>0.00059474640674045</v>
       </c>
       <c r="C52" t="n">
-        <v>0.00182478165204805</v>
+        <v>0.00098480279634338</v>
       </c>
       <c r="D52" t="n">
-        <v>1.29844800508057</v>
+        <v>1.933660837158795</v>
       </c>
       <c r="E52" t="n">
-        <v>-0.9372059139263799</v>
+        <v>-0.8056541746330357</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8507463389496914</v>
+        <v>0.8419122339929831</v>
       </c>
       <c r="G52" t="n">
-        <v>-0.849191211561905</v>
+        <v>-0.7595033624293496</v>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -1995,26 +1995,26 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.7915912643444445</v>
+        <v>0.7213745462093388</v>
       </c>
       <c r="C53" t="n">
-        <v>0.719671816228225</v>
+        <v>0.6533848384285768</v>
       </c>
       <c r="D53" t="n">
-        <v>3.130743645301167</v>
+        <v>3.402463755758265</v>
       </c>
       <c r="E53" t="n">
-        <v>0.7436706138012272</v>
+        <v>0.6477964609707972</v>
       </c>
       <c r="F53" t="n">
-        <v>0.619139152936413</v>
+        <v>0.4954540250526658</v>
       </c>
       <c r="G53" t="n">
-        <v>0.7942274651293951</v>
+        <v>0.7067182344868848</v>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2025,26 +2025,26 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8846912105461584</v>
+        <v>0.8943986241194237</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8405409622767411</v>
+        <v>0.8510824824032194</v>
       </c>
       <c r="D54" t="n">
-        <v>0.2874953783992834</v>
+        <v>0.2872390528231403</v>
       </c>
       <c r="E54" t="n">
-        <v>0.8352150783562517</v>
+        <v>0.84589032302788</v>
       </c>
       <c r="F54" t="n">
-        <v>0.810099523328619</v>
+        <v>0.7972723125711829</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8859002020870177</v>
+        <v>0.889862995174439</v>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2055,26 +2055,26 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8340278395540249</v>
+        <v>0.8584589332689448</v>
       </c>
       <c r="C55" t="n">
-        <v>0.7698049523525573</v>
+        <v>0.8058887800361672</v>
       </c>
       <c r="D55" t="n">
-        <v>0.05230426479677074</v>
+        <v>0.05200082025686396</v>
       </c>
       <c r="E55" t="n">
-        <v>0.7275587739071838</v>
+        <v>0.8117115412523335</v>
       </c>
       <c r="F55" t="n">
-        <v>0.5398268822283023</v>
+        <v>0.706344770085169</v>
       </c>
       <c r="G55" t="n">
-        <v>0.7783868997546373</v>
+        <v>0.8529278071666788</v>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2085,26 +2085,26 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7022199206157573</v>
+        <v>0.7082236187184148</v>
       </c>
       <c r="C56" t="n">
-        <v>0.6559390849073805</v>
+        <v>0.6503934647566005</v>
       </c>
       <c r="D56" t="n">
-        <v>24.67305666065167</v>
+        <v>24.23094943653339</v>
       </c>
       <c r="E56" t="n">
-        <v>0.4040839897124238</v>
+        <v>0.5086065120851192</v>
       </c>
       <c r="F56" t="n">
-        <v>0.02552744322533394</v>
+        <v>0.1821680624872614</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4493916682687953</v>
+        <v>0.5630669716098132</v>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2115,26 +2115,26 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7501769624725184</v>
+        <v>0.7424881495507631</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6811899278408025</v>
+        <v>0.6980547586235714</v>
       </c>
       <c r="D57" t="n">
-        <v>0.03544709714181936</v>
+        <v>0.03466849920260484</v>
       </c>
       <c r="E57" t="n">
-        <v>0.6938630702686907</v>
+        <v>0.6524957900436589</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6474829029671523</v>
+        <v>0.5473826480699613</v>
       </c>
       <c r="G57" t="n">
-        <v>0.7434779767251887</v>
+        <v>0.7033483858810219</v>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2145,26 +2145,26 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.7090929693688657</v>
+        <v>0.7539969584905981</v>
       </c>
       <c r="C58" t="n">
-        <v>0.6522632532249242</v>
+        <v>0.6921071601672594</v>
       </c>
       <c r="D58" t="n">
-        <v>0.2871446992391608</v>
+        <v>0.2874977553576155</v>
       </c>
       <c r="E58" t="n">
-        <v>0.5903553701381405</v>
+        <v>0.6251433070571104</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5333763067591557</v>
+        <v>0.5865946994224028</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6886895386343974</v>
+        <v>0.7315303194914696</v>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2175,26 +2175,26 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.9254251970838787</v>
+        <v>0.9010502315020736</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8879111256846424</v>
+        <v>0.856993182100784</v>
       </c>
       <c r="D59" t="n">
-        <v>0.00316484863954621</v>
+        <v>0.00886750307828247</v>
       </c>
       <c r="E59" t="n">
-        <v>0.934065531785516</v>
+        <v>0.8852480824520292</v>
       </c>
       <c r="F59" t="n">
-        <v>0.8838510867024645</v>
+        <v>0.8082415175630335</v>
       </c>
       <c r="G59" t="n">
-        <v>0.9489593888775207</v>
+        <v>0.9111398728348606</v>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2205,26 +2205,26 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.9686106063109202</v>
+        <v>0.6733640237729119</v>
       </c>
       <c r="C60" t="n">
-        <v>0.9462558356289652</v>
+        <v>0.6247754571158789</v>
       </c>
       <c r="D60" t="n">
-        <v>0.00037623663048139</v>
+        <v>0.00121237063272356</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9635915513003313</v>
+        <v>0.4630106255110088</v>
       </c>
       <c r="F60" t="n">
-        <v>0.9380483550268159</v>
+        <v>0.214220790029365</v>
       </c>
       <c r="G60" t="n">
-        <v>0.9727528827466606</v>
+        <v>0.5285338474402911</v>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2235,26 +2235,26 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.751422689321252</v>
+        <v>0.899084264213126</v>
       </c>
       <c r="C61" t="n">
-        <v>0.6835472979259376</v>
+        <v>0.8680314474826241</v>
       </c>
       <c r="D61" t="n">
-        <v>2.722393821507904</v>
+        <v>3.244318877988471</v>
       </c>
       <c r="E61" t="n">
-        <v>0.6657621225102027</v>
+        <v>0.8400802704501862</v>
       </c>
       <c r="F61" t="n">
-        <v>0.4099992267592877</v>
+        <v>0.6941332838344438</v>
       </c>
       <c r="G61" t="n">
-        <v>0.7078377740811137</v>
+        <v>0.8608111452809603</v>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>medicalAbstracts</t>
+          <t>syntheticCareHomeNurseNotes</t>
         </is>
       </c>
     </row>
@@ -2265,26 +2265,26 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>6.608293408227e-05</v>
+        <v>4.956220056169e-05</v>
       </c>
       <c r="C62" t="n">
-        <v>0.00011585915251098</v>
+        <v>8.689436438323001e-05</v>
       </c>
       <c r="D62" t="n">
-        <v>1.720589589786607</v>
+        <v>1.64878514191245</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.8642801580041883</v>
+        <v>-0.5586091155044843</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7840651165300758</v>
+        <v>0.9480101249712269</v>
       </c>
       <c r="G62" t="n">
-        <v>-0.8281983624901756</v>
+        <v>-0.4302643439198702</v>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2295,26 +2295,26 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8665474208593323</v>
+        <v>0.787055263971669</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8097852752276364</v>
+        <v>0.7193066370657968</v>
       </c>
       <c r="D63" t="n">
-        <v>3.405885065566514</v>
+        <v>3.147568300179218</v>
       </c>
       <c r="E63" t="n">
-        <v>0.840572377971998</v>
+        <v>0.7562806050934462</v>
       </c>
       <c r="F63" t="n">
-        <v>0.6805219650084613</v>
+        <v>0.5487746253654227</v>
       </c>
       <c r="G63" t="n">
-        <v>0.844516103735931</v>
+        <v>0.7767629806210856</v>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2325,26 +2325,26 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.6578085882397794</v>
+        <v>0.8582409866690388</v>
       </c>
       <c r="C64" t="n">
-        <v>0.5751375060368658</v>
+        <v>0.806964557451171</v>
       </c>
       <c r="D64" t="n">
-        <v>0.2872256370999585</v>
+        <v>0.2875257597432571</v>
       </c>
       <c r="E64" t="n">
-        <v>0.6332356570445389</v>
+        <v>0.8421962474171353</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6373124735021976</v>
+        <v>0.8298596586822343</v>
       </c>
       <c r="G64" t="n">
-        <v>0.7234168122961825</v>
+        <v>0.8943727476581658</v>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2355,26 +2355,26 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.9251013483460204</v>
+        <v>0.8643502692032348</v>
       </c>
       <c r="C65" t="n">
-        <v>0.8871078412154333</v>
+        <v>0.8145123145129167</v>
       </c>
       <c r="D65" t="n">
-        <v>0.0535231050432689</v>
+        <v>0.05166617002853256</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8649979511229582</v>
+        <v>0.8340277743129106</v>
       </c>
       <c r="F65" t="n">
-        <v>0.8125829459328547</v>
+        <v>0.7642540694659509</v>
       </c>
       <c r="G65" t="n">
-        <v>0.9065884019552606</v>
+        <v>0.876582109105865</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2385,26 +2385,26 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7470383408100243</v>
+        <v>0.7579197854846293</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6905108964582449</v>
+        <v>0.6980569298133102</v>
       </c>
       <c r="D66" t="n">
-        <v>24.47792528537583</v>
+        <v>24.82748105517844</v>
       </c>
       <c r="E66" t="n">
-        <v>0.5118131174625544</v>
+        <v>0.724567988734647</v>
       </c>
       <c r="F66" t="n">
-        <v>0.2463872111346738</v>
+        <v>0.6161429724142076</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5956368885492256</v>
+        <v>0.7948442333279333</v>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2415,26 +2415,26 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.9124228502925016</v>
+        <v>0.8217297419800311</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8624673181991801</v>
+        <v>0.753526750849542</v>
       </c>
       <c r="D67" t="n">
-        <v>0.03587055599708034</v>
+        <v>0.03388586007287284</v>
       </c>
       <c r="E67" t="n">
-        <v>0.9034009552803535</v>
+        <v>0.8226725565584385</v>
       </c>
       <c r="F67" t="n">
-        <v>0.8558657959898701</v>
+        <v>0.7466732775740352</v>
       </c>
       <c r="G67" t="n">
-        <v>0.9197572642788061</v>
+        <v>0.8486213719879085</v>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2445,26 +2445,26 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7676561103415556</v>
+        <v>0.6983013297072442</v>
       </c>
       <c r="C68" t="n">
-        <v>0.7067963378066315</v>
+        <v>0.6444345646817389</v>
       </c>
       <c r="D68" t="n">
-        <v>0.2874684338624121</v>
+        <v>0.2875176632810553</v>
       </c>
       <c r="E68" t="n">
-        <v>0.6507616379282484</v>
+        <v>0.5318367146060889</v>
       </c>
       <c r="F68" t="n">
-        <v>0.6232830542148122</v>
+        <v>0.4946255682134423</v>
       </c>
       <c r="G68" t="n">
-        <v>0.7247072972794082</v>
+        <v>0.666444458423916</v>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2475,26 +2475,26 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.9651477123020159</v>
+        <v>0.7608526392930821</v>
       </c>
       <c r="C69" t="n">
-        <v>0.9452136057948701</v>
+        <v>0.6953079240660907</v>
       </c>
       <c r="D69" t="n">
-        <v>0.00487208103850372</v>
+        <v>0.00710288943866135</v>
       </c>
       <c r="E69" t="n">
-        <v>0.9324766616057527</v>
+        <v>0.73278502515823</v>
       </c>
       <c r="F69" t="n">
-        <v>0.8777896208063263</v>
+        <v>0.5634318822607469</v>
       </c>
       <c r="G69" t="n">
-        <v>0.9466284472699473</v>
+        <v>0.7737342321612199</v>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2505,26 +2505,26 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.9538869261692655</v>
+        <v>0.8559280839761594</v>
       </c>
       <c r="C70" t="n">
-        <v>0.927799043608734</v>
+        <v>0.8040882840838266</v>
       </c>
       <c r="D70" t="n">
-        <v>0.00074904643773715</v>
+        <v>0.0007249781767510201</v>
       </c>
       <c r="E70" t="n">
-        <v>0.9457955674419738</v>
+        <v>0.8196113473661391</v>
       </c>
       <c r="F70" t="n">
-        <v>0.9112190565585752</v>
+        <v>0.6824371564544203</v>
       </c>
       <c r="G70" t="n">
-        <v>0.9596533681218674</v>
+        <v>0.8496949728216818</v>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2535,26 +2535,26 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.9840241329791966</v>
+        <v>0.883818894635845</v>
       </c>
       <c r="C71" t="n">
-        <v>0.9736638088063496</v>
+        <v>0.8480012893674259</v>
       </c>
       <c r="D71" t="n">
-        <v>2.920342613853209</v>
+        <v>2.964079712475722</v>
       </c>
       <c r="E71" t="n">
-        <v>0.9322702400885894</v>
+        <v>0.8078311867680248</v>
       </c>
       <c r="F71" t="n">
-        <v>0.862760716321628</v>
+        <v>0.6108978286530231</v>
       </c>
       <c r="G71" t="n">
-        <v>0.9446140385083324</v>
+        <v>0.8241501296232097</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>simSUM</t>
+          <t>clinicalDialogueSummarizations</t>
         </is>
       </c>
     </row>
@@ -2565,26 +2565,26 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.00059474640674045</v>
+        <v>6.608293408227e-05</v>
       </c>
       <c r="C72" t="n">
-        <v>0.00098480279634338</v>
+        <v>0.00011585915251098</v>
       </c>
       <c r="D72" t="n">
-        <v>1.933660837158795</v>
+        <v>1.720589589786607</v>
       </c>
       <c r="E72" t="n">
-        <v>-0.8056541746330357</v>
+        <v>-0.8642801580041883</v>
       </c>
       <c r="F72" t="n">
-        <v>0.8419122339929831</v>
+        <v>0.7840651165300758</v>
       </c>
       <c r="G72" t="n">
-        <v>-0.7595033624293496</v>
+        <v>-0.8281983624901756</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2595,26 +2595,26 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7213745462093388</v>
+        <v>0.8665474208593323</v>
       </c>
       <c r="C73" t="n">
-        <v>0.6533848384285768</v>
+        <v>0.8097852752276364</v>
       </c>
       <c r="D73" t="n">
-        <v>3.402463755758265</v>
+        <v>3.405885065566514</v>
       </c>
       <c r="E73" t="n">
-        <v>0.6477964609707972</v>
+        <v>0.840572377971998</v>
       </c>
       <c r="F73" t="n">
-        <v>0.4954540250526658</v>
+        <v>0.6805219650084613</v>
       </c>
       <c r="G73" t="n">
-        <v>0.7067182344868848</v>
+        <v>0.844516103735931</v>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2625,26 +2625,26 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.8943986241194237</v>
+        <v>0.6578085882397794</v>
       </c>
       <c r="C74" t="n">
-        <v>0.8510824824032194</v>
+        <v>0.5751375060368658</v>
       </c>
       <c r="D74" t="n">
-        <v>0.2872390528231403</v>
+        <v>0.2872256370999585</v>
       </c>
       <c r="E74" t="n">
-        <v>0.84589032302788</v>
+        <v>0.6332356570445389</v>
       </c>
       <c r="F74" t="n">
-        <v>0.7972723125711829</v>
+        <v>0.6373124735021976</v>
       </c>
       <c r="G74" t="n">
-        <v>0.889862995174439</v>
+        <v>0.7234168122961825</v>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2655,26 +2655,26 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.8584589332689448</v>
+        <v>0.9251013483460204</v>
       </c>
       <c r="C75" t="n">
-        <v>0.8058887800361672</v>
+        <v>0.8871078412154333</v>
       </c>
       <c r="D75" t="n">
-        <v>0.05200082025686396</v>
+        <v>0.0535231050432689</v>
       </c>
       <c r="E75" t="n">
-        <v>0.8117115412523335</v>
+        <v>0.8649979511229582</v>
       </c>
       <c r="F75" t="n">
-        <v>0.706344770085169</v>
+        <v>0.8125829459328547</v>
       </c>
       <c r="G75" t="n">
-        <v>0.8529278071666788</v>
+        <v>0.9065884019552606</v>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2685,26 +2685,26 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.7082236187184148</v>
+        <v>0.7470383408100243</v>
       </c>
       <c r="C76" t="n">
-        <v>0.6503934647566005</v>
+        <v>0.6905108964582449</v>
       </c>
       <c r="D76" t="n">
-        <v>24.23094943653339</v>
+        <v>24.47792528537583</v>
       </c>
       <c r="E76" t="n">
-        <v>0.5086065120851192</v>
+        <v>0.5118131174625544</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1821680624872614</v>
+        <v>0.2463872111346738</v>
       </c>
       <c r="G76" t="n">
-        <v>0.5630669716098132</v>
+        <v>0.5956368885492256</v>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2715,26 +2715,26 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.7424881495507631</v>
+        <v>0.9124228502925016</v>
       </c>
       <c r="C77" t="n">
-        <v>0.6980547586235714</v>
+        <v>0.8624673181991801</v>
       </c>
       <c r="D77" t="n">
-        <v>0.03466849920260484</v>
+        <v>0.03587055599708034</v>
       </c>
       <c r="E77" t="n">
-        <v>0.6524957900436589</v>
+        <v>0.9034009552803535</v>
       </c>
       <c r="F77" t="n">
-        <v>0.5473826480699613</v>
+        <v>0.8558657959898701</v>
       </c>
       <c r="G77" t="n">
-        <v>0.7033483858810219</v>
+        <v>0.9197572642788061</v>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2745,26 +2745,26 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.7539969584905981</v>
+        <v>0.7676561103415556</v>
       </c>
       <c r="C78" t="n">
-        <v>0.6921071601672594</v>
+        <v>0.7067963378066315</v>
       </c>
       <c r="D78" t="n">
-        <v>0.2874977553576155</v>
+        <v>0.2874684338624121</v>
       </c>
       <c r="E78" t="n">
-        <v>0.6251433070571104</v>
+        <v>0.6507616379282484</v>
       </c>
       <c r="F78" t="n">
-        <v>0.5865946994224028</v>
+        <v>0.6232830542148122</v>
       </c>
       <c r="G78" t="n">
-        <v>0.7315303194914696</v>
+        <v>0.7247072972794082</v>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2775,26 +2775,26 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.9010502315020736</v>
+        <v>0.9651477123020159</v>
       </c>
       <c r="C79" t="n">
-        <v>0.856993182100784</v>
+        <v>0.9452136057948701</v>
       </c>
       <c r="D79" t="n">
-        <v>0.00886750307828247</v>
+        <v>0.00487208103850372</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8852480824520292</v>
+        <v>0.9324766616057527</v>
       </c>
       <c r="F79" t="n">
-        <v>0.8082415175630335</v>
+        <v>0.8777896208063263</v>
       </c>
       <c r="G79" t="n">
-        <v>0.9111398728348606</v>
+        <v>0.9466284472699473</v>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2805,26 +2805,26 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6733640237729119</v>
+        <v>0.9538869261692655</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6247754571158789</v>
+        <v>0.927799043608734</v>
       </c>
       <c r="D80" t="n">
-        <v>0.00121237063272356</v>
+        <v>0.00074904643773715</v>
       </c>
       <c r="E80" t="n">
-        <v>0.4630106255110088</v>
+        <v>0.9457955674419738</v>
       </c>
       <c r="F80" t="n">
-        <v>0.214220790029365</v>
+        <v>0.9112190565585752</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5285338474402911</v>
+        <v>0.9596533681218674</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2835,26 +2835,26 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.899084264213126</v>
+        <v>0.9840241329791966</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8680314474826241</v>
+        <v>0.9736638088063496</v>
       </c>
       <c r="D81" t="n">
-        <v>3.244318877988471</v>
+        <v>2.920342613853209</v>
       </c>
       <c r="E81" t="n">
-        <v>0.8400802704501862</v>
+        <v>0.9322702400885894</v>
       </c>
       <c r="F81" t="n">
-        <v>0.6941332838344438</v>
+        <v>0.862760716321628</v>
       </c>
       <c r="G81" t="n">
-        <v>0.8608111452809603</v>
+        <v>0.9446140385083324</v>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>syntheticCareHomeNurseNotes</t>
+          <t>simSUM</t>
         </is>
       </c>
     </row>
@@ -2865,26 +2865,26 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>1.652073352056e-05</v>
+        <v>0.00089211961011067</v>
       </c>
       <c r="C82" t="n">
-        <v>2.896478812774e-05</v>
+        <v>0.00146272180045121</v>
       </c>
       <c r="D82" t="n">
-        <v>1.537187658337917</v>
+        <v>4.395724263562654</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.3242384694860216</v>
+        <v>-0.809484351466615</v>
       </c>
       <c r="F82" t="n">
-        <v>0.9999943187021736</v>
+        <v>0.7627224203800828</v>
       </c>
       <c r="G82" t="n">
-        <v>-0.4041739582825991</v>
+        <v>-0.6959813022058214</v>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2895,26 +2895,26 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.799564318604464</v>
+        <v>0.7972782091524864</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7397077370603085</v>
+        <v>0.7240479319803135</v>
       </c>
       <c r="D83" t="n">
-        <v>3.094511333841504</v>
+        <v>3.350735583803054</v>
       </c>
       <c r="E83" t="n">
-        <v>0.7475706095004031</v>
+        <v>0.7905378245824863</v>
       </c>
       <c r="F83" t="n">
-        <v>0.5845641257904433</v>
+        <v>0.6531961737880122</v>
       </c>
       <c r="G83" t="n">
-        <v>0.7873153688078518</v>
+        <v>0.8278155976895829</v>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2925,26 +2925,26 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.8910154744203977</v>
+        <v>0.8339028750312412</v>
       </c>
       <c r="C84" t="n">
-        <v>0.8440676538810776</v>
+        <v>0.7868661130217655</v>
       </c>
       <c r="D84" t="n">
-        <v>0.2874102313131758</v>
+        <v>0.2879106905600148</v>
       </c>
       <c r="E84" t="n">
-        <v>0.890335074836328</v>
+        <v>0.8083300428086495</v>
       </c>
       <c r="F84" t="n">
-        <v>0.8664774250874285</v>
+        <v>0.7998673612066989</v>
       </c>
       <c r="G84" t="n">
-        <v>0.9220606499519557</v>
+        <v>0.8727572474710856</v>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2955,26 +2955,26 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.8039953699585287</v>
+        <v>0.8985553889361919</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7432767346457733</v>
+        <v>0.8557477244856269</v>
       </c>
       <c r="D85" t="n">
-        <v>0.05400749463438276</v>
+        <v>0.05326363144688817</v>
       </c>
       <c r="E85" t="n">
-        <v>0.6093745138115961</v>
+        <v>0.9094688928370712</v>
       </c>
       <c r="F85" t="n">
-        <v>0.2901694783353826</v>
+        <v>0.9011702183856649</v>
       </c>
       <c r="G85" t="n">
-        <v>0.6455485223170351</v>
+        <v>0.9354738333338757</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -2985,26 +2985,26 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6762388432097668</v>
+        <v>0.7834869973355021</v>
       </c>
       <c r="C86" t="n">
-        <v>0.6184872919050513</v>
+        <v>0.715529675038251</v>
       </c>
       <c r="D86" t="n">
-        <v>24.55161798998138</v>
+        <v>23.91773641731701</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3925463826515103</v>
+        <v>0.7708915358075382</v>
       </c>
       <c r="F86" t="n">
-        <v>0.003728178356317342</v>
+        <v>0.688555444341609</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4379273084962533</v>
+        <v>0.8306302600021064</v>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3015,26 +3015,26 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.835299512426557</v>
+        <v>0.8770188124557858</v>
       </c>
       <c r="C87" t="n">
-        <v>0.7691182987506945</v>
+        <v>0.8257382927914406</v>
       </c>
       <c r="D87" t="n">
-        <v>0.034947455732596</v>
+        <v>0.03762417097754026</v>
       </c>
       <c r="E87" t="n">
-        <v>0.83291343456331</v>
+        <v>0.8813483683856378</v>
       </c>
       <c r="F87" t="n">
-        <v>0.7770029577288198</v>
+        <v>0.843292893889229</v>
       </c>
       <c r="G87" t="n">
-        <v>0.8438361863811921</v>
+        <v>0.8945059627066803</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3045,26 +3045,26 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.7658589510605041</v>
+        <v>0.7259570376206754</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7021310812379904</v>
+        <v>0.6672952583032233</v>
       </c>
       <c r="D88" t="n">
-        <v>0.287340523633405</v>
+        <v>0.2878869578316642</v>
       </c>
       <c r="E88" t="n">
-        <v>0.6212491799343089</v>
+        <v>0.609632985921752</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5200350093128089</v>
+        <v>0.5323725446540942</v>
       </c>
       <c r="G88" t="n">
-        <v>0.7142029392442806</v>
+        <v>0.7044284666259213</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3075,26 +3075,26 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.8972271643219933</v>
+        <v>0.8593014906784939</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8499122795159562</v>
+        <v>0.8049421142108586</v>
       </c>
       <c r="D89" t="n">
-        <v>0.00691691329316514</v>
+        <v>0.01200148696040652</v>
       </c>
       <c r="E89" t="n">
-        <v>0.8600772645940997</v>
+        <v>0.8530232373602328</v>
       </c>
       <c r="F89" t="n">
-        <v>0.7676097144197198</v>
+        <v>0.7278409207550676</v>
       </c>
       <c r="G89" t="n">
-        <v>0.8907185934374053</v>
+        <v>0.8746235855039952</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3105,26 +3105,26 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.8646572795011586</v>
+        <v>0.8952445703973873</v>
       </c>
       <c r="C90" t="n">
-        <v>0.8045616759013472</v>
+        <v>0.8463602451357246</v>
       </c>
       <c r="D90" t="n">
-        <v>0.00100905166567283</v>
+        <v>0.00162688916015331</v>
       </c>
       <c r="E90" t="n">
-        <v>0.8380571833348966</v>
+        <v>0.8925427165675154</v>
       </c>
       <c r="F90" t="n">
-        <v>0.7193780293016363</v>
+        <v>0.8321655686765648</v>
       </c>
       <c r="G90" t="n">
-        <v>0.8666304329210359</v>
+        <v>0.9198972906206533</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
@@ -3135,26 +3135,26 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.9189985258422397</v>
+        <v>0.8402753243782486</v>
       </c>
       <c r="C91" t="n">
-        <v>0.8792521164110203</v>
+        <v>0.7902984325492859</v>
       </c>
       <c r="D91" t="n">
-        <v>2.932961144099852</v>
+        <v>6.818805731702736</v>
       </c>
       <c r="E91" t="n">
-        <v>0.9139324333961106</v>
+        <v>0.5823835570330234</v>
       </c>
       <c r="F91" t="n">
-        <v>0.8486291493829754</v>
+        <v>0.2331710977408832</v>
       </c>
       <c r="G91" t="n">
-        <v>0.9341400061572518</v>
+        <v>0.6154569934467748</v>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>yahoo</t>
+          <t>atis</t>
         </is>
       </c>
     </row>
